--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务支持RC隔离级别测试场景.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/事务支持RC隔离级别测试场景.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="隔离级别基本测试场景" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="263">
   <si>
     <t>操作步骤</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1954,10 +1954,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.考虑插入的记录存在索引、不存在索引2种情况；2.同时考虑事务回滚的场景(3*4个用例)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.考虑更新字段存在索引、不存在索引2种情况；2.同时考虑事务回滚的场景(3*4个用例)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2091,11 +2087,6 @@
   </si>
   <si>
     <t>2.事务1中删除记录R1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务提交，则读到R1及R2
-事务回滚，则读到R1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3535,1446 +3526,1427 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>场景7：插入记录与其他事务中更新的记录重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景9：更新已提交记录与已提交记录唯一索引重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景10：更新已提交记录与本事务中插入的记录唯一索引重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景11：更新已提交记录与本事务中更新的记录唯一索引重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景12：更新已提交记录与本事务中删除的记录唯一索引重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景13：更新已提交记录与其他事务插入的记录重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景14：更新已提交记录与其他事务更新的记录重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景15：更新已提交记录与其他事务删除的记录重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景16：回滚的记录与已提交记录唯一索引重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景17：回滚的记录与本事务中的记录重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景18：回滚的记录与其他事务的记录重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景1：创建索引与事务并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景1：删除索引与事务并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景9：批量CUD操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中存在大量记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>执行批量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>CUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>操作</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读到步骤1及步骤2中未提交的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读到步骤1中的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景10：事务中多次更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>执行多次更新操作，例如：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R4…</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读到步骤2中更新后的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引创建失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景1：插入并发，过程中读</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景2：插入与更新并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景3：插入与删除并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景4：更新并发-匹配更新前记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景5：更新并发-匹配更新后记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景6：更新与插入并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景7：更新与删除并发--匹配更新前记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景8：更新与删除并发--匹配更新后记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景9：删除并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景10：删除与插入并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景11：删除与更新并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中已存在记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读到R1，不放锁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中已存在记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（通过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>mysql</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>select for update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景12：读并发与更新并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务3返回结果，R1更新为R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1更新为R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>select for update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>及事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>均提交</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提交事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，记录读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务3返回结果，R1删除成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中已存在记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（通过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>mysql</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试或者驱动进行测试）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>插入记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>删除记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.事务5记录读记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中已存在部分记录，并发执行如下事务操作</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功，立即返回</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>select</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.考虑插入的记录存在索引的情况；2.同时考虑事务回滚的场景(3*4个用例)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开启</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个并发事务操作</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>插入记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景13：并发读写不同记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>场景6：插入记录与其他事务中更新的记录重复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>场景7：插入记录与其他事务中更新的记录重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>场景8：插入记录与其他事务中删除的记录重复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>场景9：更新已提交记录与已提交记录唯一索引重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景10：更新已提交记录与本事务中插入的记录唯一索引重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景11：更新已提交记录与本事务中更新的记录唯一索引重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景12：更新已提交记录与本事务中删除的记录唯一索引重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景13：更新已提交记录与其他事务插入的记录重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景14：更新已提交记录与其他事务更新的记录重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景15：更新已提交记录与其他事务删除的记录重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景16：回滚的记录与已提交记录唯一索引重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景17：回滚的记录与本事务中的记录重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景18：回滚的记录与其他事务的记录重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景1：创建索引与事务并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景1：删除索引与事务并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景9：批量CUD操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>集合中存在大量记录</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>执行批量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>CUD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>操作</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读到步骤1及步骤2中未提交的记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读到步骤1中的记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景10：事务中多次更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>执行多次更新操作，例如：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>更新为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>更新为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>更新为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R4…</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读到步骤2中更新后的记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索引创建失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景1：插入并发，过程中读</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景2：插入与更新并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景3：插入与删除并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景4：更新并发-匹配更新前记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景5：更新并发-匹配更新后记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景6：更新与插入并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景7：更新与删除并发--匹配更新前记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景8：更新与删除并发--匹配更新后记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景9：删除并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景10：删除与插入并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景11：删除与更新并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>集合中已存在记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读到R1，不放锁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>集合中已存在记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（通过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>mysql</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测试）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>select for update</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录读记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景12：读并发与更新并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>更新记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R2</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务3返回结果，R1更新为R2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R1更新为R2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>select for update</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录读记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>及事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>均提交</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>删除记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R1删除成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>更新记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>提交事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，记录读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引读</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>回滚事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，记录读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引读</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>删除</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事务3返回结果，R1删除成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>集合中已存在记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（通过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>mysql</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测试或者驱动进行测试）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景14：并发读写不同记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>插入记录</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>更新记录</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>删除记录</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引读记录</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.事务5记录读记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>集合中已存在部分记录，并发执行如下事务操作</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成功，立即返回</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景13：读并发与删除并发(RC隔离级别)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事务</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>select</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引读</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录读记录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>R1</t>
-    </r>
+    <t>1.存在记录R1、R2，_id字段重复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5174,20 +5146,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -5198,34 +5192,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5531,13 +5503,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -5563,7 +5535,7 @@
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -5579,7 +5551,7 @@
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>10</v>
@@ -5603,7 +5575,7 @@
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -5612,13 +5584,13 @@
     <row r="9" spans="1:4" ht="30" customHeight="1"/>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B10" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
       <c r="A11" s="3" t="s">
@@ -5644,7 +5616,7 @@
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -5660,7 +5632,7 @@
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
@@ -5684,7 +5656,7 @@
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5693,13 +5665,13 @@
     <row r="18" spans="1:4" ht="30" customHeight="1"/>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B19" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="3" t="s">
@@ -5725,7 +5697,7 @@
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -5741,7 +5713,7 @@
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>13</v>
@@ -5765,7 +5737,7 @@
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -5774,13 +5746,13 @@
     <row r="27" spans="1:4" ht="30" customHeight="1"/>
     <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B28" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B28" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="3" t="s">
@@ -5806,7 +5778,7 @@
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -5822,7 +5794,7 @@
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>15</v>
@@ -5846,7 +5818,7 @@
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -5855,13 +5827,13 @@
     <row r="36" spans="1:4" ht="30" customHeight="1"/>
     <row r="37" spans="1:4" ht="30" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B37" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
     </row>
     <row r="38" spans="1:4" ht="30" customHeight="1">
       <c r="A38" s="3" t="s">
@@ -5887,7 +5859,7 @@
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -5903,7 +5875,7 @@
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>15</v>
@@ -5927,7 +5899,7 @@
     </row>
     <row r="44" spans="1:4" ht="30" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -5936,13 +5908,13 @@
     <row r="45" spans="1:4" ht="30" customHeight="1"/>
     <row r="46" spans="1:4" ht="30" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B46" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
     </row>
     <row r="47" spans="1:4" ht="30" customHeight="1">
       <c r="A47" s="3" t="s">
@@ -5960,7 +5932,7 @@
     </row>
     <row r="48" spans="1:4" ht="30" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -5968,35 +5940,35 @@
     </row>
     <row r="49" spans="1:4" ht="30" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="30" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="30" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -6004,7 +5976,7 @@
     </row>
     <row r="52" spans="1:4" ht="30" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -6013,13 +5985,13 @@
     <row r="53" spans="1:4" ht="30" customHeight="1"/>
     <row r="54" spans="1:4" ht="30" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B54" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B54" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
     </row>
     <row r="55" spans="1:4" ht="30" customHeight="1">
       <c r="A55" s="3" t="s">
@@ -6037,7 +6009,7 @@
     </row>
     <row r="56" spans="1:4" ht="30" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -6045,35 +6017,35 @@
     </row>
     <row r="57" spans="1:4" ht="30" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="30" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -6081,7 +6053,7 @@
     </row>
     <row r="60" spans="1:4" ht="30" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -6090,13 +6062,13 @@
     <row r="61" spans="1:4" ht="30" customHeight="1"/>
     <row r="62" spans="1:4" ht="30" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B62" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B62" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
     </row>
     <row r="63" spans="1:4" ht="30" customHeight="1">
       <c r="A63" s="3" t="s">
@@ -6114,7 +6086,7 @@
     </row>
     <row r="64" spans="1:4" ht="30" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -6122,35 +6094,35 @@
     </row>
     <row r="65" spans="1:4" ht="30" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -6158,7 +6130,7 @@
     </row>
     <row r="68" spans="1:4" ht="30" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -6167,13 +6139,13 @@
     <row r="69" spans="1:4" ht="30" customHeight="1"/>
     <row r="70" spans="1:4" ht="30" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B70" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B70" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
     </row>
     <row r="71" spans="1:4" ht="30" customHeight="1">
       <c r="A71" s="3" t="s">
@@ -6191,7 +6163,7 @@
     </row>
     <row r="72" spans="1:4" ht="30" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -6199,7 +6171,7 @@
     </row>
     <row r="73" spans="1:4" ht="30" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -6207,21 +6179,21 @@
     </row>
     <row r="74" spans="1:4" ht="30" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="30" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -6229,7 +6201,7 @@
     </row>
     <row r="76" spans="1:4" ht="30" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -6238,13 +6210,13 @@
     <row r="77" spans="1:4" ht="30" customHeight="1"/>
     <row r="78" spans="1:4" ht="30" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B78" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B78" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="20"/>
     </row>
     <row r="79" spans="1:4" ht="30" customHeight="1">
       <c r="A79" s="3" t="s">
@@ -6262,7 +6234,7 @@
     </row>
     <row r="80" spans="1:4" ht="30" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -6270,7 +6242,7 @@
     </row>
     <row r="81" spans="1:4" ht="30" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -6278,21 +6250,21 @@
     </row>
     <row r="82" spans="1:4" ht="30" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="30" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -6300,7 +6272,7 @@
     </row>
     <row r="84" spans="1:4" ht="30" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -6321,16 +6293,16 @@
     <row r="97" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B37:D37"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B70:D70"/>
     <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6340,29 +6312,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F233"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="6" width="30.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="A1" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B2" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -6380,7 +6352,7 @@
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>257</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -6388,7 +6360,7 @@
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>258</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -6465,7 +6437,7 @@
       <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="26" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -6479,7 +6451,7 @@
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="23"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="1" t="s">
         <v>38</v>
       </c>
@@ -6491,7 +6463,7 @@
       <c r="B13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="1" t="s">
         <v>29</v>
       </c>
@@ -6503,7 +6475,7 @@
       <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="23"/>
+      <c r="C14" s="26"/>
       <c r="D14" s="1" t="s">
         <v>38</v>
       </c>
@@ -6515,28 +6487,28 @@
       <c r="B15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="23"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B17" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="3" t="s">
@@ -6639,7 +6611,7 @@
       <c r="B26" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -6653,7 +6625,7 @@
       <c r="B27" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="20"/>
+      <c r="C27" s="28"/>
       <c r="D27" s="1" t="s">
         <v>41</v>
       </c>
@@ -6665,7 +6637,7 @@
       <c r="B28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="20"/>
+      <c r="C28" s="28"/>
       <c r="D28" s="1" t="s">
         <v>39</v>
       </c>
@@ -6677,7 +6649,7 @@
       <c r="B29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="20"/>
+      <c r="C29" s="28"/>
       <c r="D29" s="1" t="s">
         <v>41</v>
       </c>
@@ -6689,28 +6661,28 @@
       <c r="B30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="21"/>
+      <c r="C30" s="29"/>
       <c r="D30" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B32" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="3" t="s">
@@ -6813,7 +6785,7 @@
       <c r="B41" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -6827,7 +6799,7 @@
       <c r="B42" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="20"/>
+      <c r="C42" s="28"/>
       <c r="D42" s="1" t="s">
         <v>46</v>
       </c>
@@ -6839,7 +6811,7 @@
       <c r="B43" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="20"/>
+      <c r="C43" s="28"/>
       <c r="D43" s="1" t="s">
         <v>39</v>
       </c>
@@ -6851,7 +6823,7 @@
       <c r="B44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="20"/>
+      <c r="C44" s="28"/>
       <c r="D44" s="1" t="s">
         <v>46</v>
       </c>
@@ -6863,28 +6835,28 @@
       <c r="B45" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="21"/>
+      <c r="C45" s="29"/>
       <c r="D45" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" customHeight="1">
-      <c r="A46" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
+      <c r="A46" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
     </row>
     <row r="47" spans="1:4" ht="30" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B47" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="B47" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
     </row>
     <row r="48" spans="1:4" ht="30" customHeight="1">
       <c r="A48" s="3" t="s">
@@ -6987,7 +6959,7 @@
       <c r="B56" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="4" t="s">
@@ -7001,7 +6973,7 @@
       <c r="B57" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="20"/>
+      <c r="C57" s="28"/>
       <c r="D57" s="1" t="s">
         <v>50</v>
       </c>
@@ -7013,7 +6985,7 @@
       <c r="B58" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C58" s="20"/>
+      <c r="C58" s="28"/>
       <c r="D58" s="1" t="s">
         <v>41</v>
       </c>
@@ -7025,7 +6997,7 @@
       <c r="B59" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="20"/>
+      <c r="C59" s="28"/>
       <c r="D59" s="1" t="s">
         <v>50</v>
       </c>
@@ -7037,28 +7009,28 @@
       <c r="B60" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="21"/>
+      <c r="C60" s="29"/>
       <c r="D60" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="30" customHeight="1">
-      <c r="A61" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
+      <c r="A61" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
     </row>
     <row r="62" spans="1:4" ht="30" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B62" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
     </row>
     <row r="63" spans="1:4" ht="30" customHeight="1">
       <c r="A63" s="3" t="s">
@@ -7161,7 +7133,7 @@
       <c r="B71" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C71" s="19" t="s">
+      <c r="C71" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D71" s="4" t="s">
@@ -7175,7 +7147,7 @@
       <c r="B72" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C72" s="20"/>
+      <c r="C72" s="28"/>
       <c r="D72" s="1" t="s">
         <v>41</v>
       </c>
@@ -7187,7 +7159,7 @@
       <c r="B73" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C73" s="20"/>
+      <c r="C73" s="28"/>
       <c r="D73" s="1" t="s">
         <v>41</v>
       </c>
@@ -7199,7 +7171,7 @@
       <c r="B74" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C74" s="20"/>
+      <c r="C74" s="28"/>
       <c r="D74" s="1" t="s">
         <v>41</v>
       </c>
@@ -7211,28 +7183,28 @@
       <c r="B75" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C75" s="21"/>
+      <c r="C75" s="29"/>
       <c r="D75" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="30" customHeight="1">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B76" s="18"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
+      <c r="B76" s="31"/>
+      <c r="C76" s="31"/>
+      <c r="D76" s="31"/>
     </row>
     <row r="77" spans="1:4" ht="30" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B77" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
     </row>
     <row r="78" spans="1:4" ht="30" customHeight="1">
       <c r="A78" s="3" t="s">
@@ -7335,7 +7307,7 @@
       <c r="B86" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="26" t="s">
         <v>36</v>
       </c>
       <c r="D86" s="4" t="s">
@@ -7349,7 +7321,7 @@
       <c r="B87" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C87" s="23"/>
+      <c r="C87" s="26"/>
       <c r="D87" s="1" t="s">
         <v>53</v>
       </c>
@@ -7361,7 +7333,7 @@
       <c r="B88" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C88" s="23"/>
+      <c r="C88" s="26"/>
       <c r="D88" s="1" t="s">
         <v>41</v>
       </c>
@@ -7373,7 +7345,7 @@
       <c r="B89" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C89" s="23"/>
+      <c r="C89" s="26"/>
       <c r="D89" s="1" t="s">
         <v>53</v>
       </c>
@@ -7385,28 +7357,28 @@
       <c r="B90" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C90" s="23"/>
+      <c r="C90" s="26"/>
       <c r="D90" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="30" customHeight="1">
-      <c r="A91" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
+      <c r="A91" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B91" s="31"/>
+      <c r="C91" s="31"/>
+      <c r="D91" s="31"/>
     </row>
     <row r="92" spans="1:4" ht="30" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B92" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B92" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
     </row>
     <row r="93" spans="1:4" ht="30" customHeight="1">
       <c r="A93" s="3" t="s">
@@ -7509,7 +7481,7 @@
       <c r="B101" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D101" s="4" t="s">
@@ -7523,7 +7495,7 @@
       <c r="B102" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C102" s="20"/>
+      <c r="C102" s="28"/>
       <c r="D102" s="1" t="s">
         <v>41</v>
       </c>
@@ -7535,7 +7507,7 @@
       <c r="B103" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C103" s="20"/>
+      <c r="C103" s="28"/>
       <c r="D103" s="1" t="s">
         <v>41</v>
       </c>
@@ -7547,7 +7519,7 @@
       <c r="B104" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C104" s="20"/>
+      <c r="C104" s="28"/>
       <c r="D104" s="1" t="s">
         <v>32</v>
       </c>
@@ -7559,28 +7531,28 @@
       <c r="B105" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C105" s="21"/>
+      <c r="C105" s="29"/>
       <c r="D105" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="30" customHeight="1">
-      <c r="A106" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B106" s="18"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="18"/>
+      <c r="A106" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B106" s="31"/>
+      <c r="C106" s="31"/>
+      <c r="D106" s="31"/>
     </row>
     <row r="107" spans="1:4" ht="30" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B107" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="B107" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C107" s="22"/>
-      <c r="D107" s="22"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
     </row>
     <row r="108" spans="1:4" ht="30" customHeight="1">
       <c r="A108" s="3" t="s">
@@ -7683,7 +7655,7 @@
       <c r="B116" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C116" s="19" t="s">
+      <c r="C116" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D116" s="4" t="s">
@@ -7697,7 +7669,7 @@
       <c r="B117" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C117" s="20"/>
+      <c r="C117" s="28"/>
       <c r="D117" s="1" t="s">
         <v>41</v>
       </c>
@@ -7709,7 +7681,7 @@
       <c r="B118" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C118" s="20"/>
+      <c r="C118" s="28"/>
       <c r="D118" s="1" t="s">
         <v>41</v>
       </c>
@@ -7721,7 +7693,7 @@
       <c r="B119" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C119" s="20"/>
+      <c r="C119" s="28"/>
       <c r="D119" s="1" t="s">
         <v>41</v>
       </c>
@@ -7733,28 +7705,28 @@
       <c r="B120" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C120" s="21"/>
+      <c r="C120" s="29"/>
       <c r="D120" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="30" customHeight="1">
-      <c r="A121" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B121" s="18"/>
-      <c r="C121" s="18"/>
-      <c r="D121" s="18"/>
+      <c r="A121" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B121" s="31"/>
+      <c r="C121" s="31"/>
+      <c r="D121" s="31"/>
     </row>
     <row r="122" spans="1:4" ht="30" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B122" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B122" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C122" s="22"/>
-      <c r="D122" s="22"/>
+      <c r="C122" s="21"/>
+      <c r="D122" s="21"/>
     </row>
     <row r="123" spans="1:4" ht="30" customHeight="1">
       <c r="A123" s="3" t="s">
@@ -7857,7 +7829,7 @@
       <c r="B131" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C131" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D131" s="4" t="s">
@@ -7871,7 +7843,7 @@
       <c r="B132" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C132" s="20"/>
+      <c r="C132" s="28"/>
       <c r="D132" s="1" t="s">
         <v>46</v>
       </c>
@@ -7883,7 +7855,7 @@
       <c r="B133" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C133" s="20"/>
+      <c r="C133" s="28"/>
       <c r="D133" s="1" t="s">
         <v>46</v>
       </c>
@@ -7895,7 +7867,7 @@
       <c r="B134" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C134" s="20"/>
+      <c r="C134" s="28"/>
       <c r="D134" s="1" t="s">
         <v>46</v>
       </c>
@@ -7907,28 +7879,28 @@
       <c r="B135" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C135" s="21"/>
+      <c r="C135" s="29"/>
       <c r="D135" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="30" customHeight="1">
-      <c r="A136" s="17" t="s">
+      <c r="A136" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="B136" s="18"/>
-      <c r="C136" s="18"/>
-      <c r="D136" s="18"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="31"/>
+      <c r="D136" s="31"/>
     </row>
     <row r="137" spans="1:4" ht="30" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B137" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B137" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C137" s="22"/>
-      <c r="D137" s="22"/>
+      <c r="C137" s="21"/>
+      <c r="D137" s="21"/>
     </row>
     <row r="138" spans="1:4" ht="30" customHeight="1">
       <c r="A138" s="3" t="s">
@@ -8031,7 +8003,7 @@
       <c r="B146" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C146" s="19" t="s">
+      <c r="C146" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D146" s="4" t="s">
@@ -8045,7 +8017,7 @@
       <c r="B147" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C147" s="20"/>
+      <c r="C147" s="28"/>
       <c r="D147" s="1" t="s">
         <v>41</v>
       </c>
@@ -8057,7 +8029,7 @@
       <c r="B148" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C148" s="20"/>
+      <c r="C148" s="28"/>
       <c r="D148" s="1" t="s">
         <v>32</v>
       </c>
@@ -8069,7 +8041,7 @@
       <c r="B149" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C149" s="20"/>
+      <c r="C149" s="28"/>
       <c r="D149" s="1" t="s">
         <v>41</v>
       </c>
@@ -8081,28 +8053,28 @@
       <c r="B150" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C150" s="21"/>
+      <c r="C150" s="29"/>
       <c r="D150" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="30" customHeight="1">
-      <c r="A151" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B151" s="18"/>
-      <c r="C151" s="18"/>
-      <c r="D151" s="18"/>
+      <c r="A151" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B151" s="31"/>
+      <c r="C151" s="31"/>
+      <c r="D151" s="31"/>
     </row>
     <row r="152" spans="1:4" ht="30" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B152" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B152" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C152" s="22"/>
-      <c r="D152" s="22"/>
+      <c r="C152" s="21"/>
+      <c r="D152" s="21"/>
     </row>
     <row r="153" spans="1:4" ht="30" customHeight="1">
       <c r="A153" s="3" t="s">
@@ -8205,7 +8177,7 @@
       <c r="B161" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C161" s="19" t="s">
+      <c r="C161" s="27" t="s">
         <v>36</v>
       </c>
       <c r="D161" s="4" t="s">
@@ -8219,7 +8191,7 @@
       <c r="B162" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C162" s="20"/>
+      <c r="C162" s="28"/>
       <c r="D162" s="4" t="s">
         <v>32</v>
       </c>
@@ -8231,7 +8203,7 @@
       <c r="B163" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C163" s="20"/>
+      <c r="C163" s="28"/>
       <c r="D163" s="4" t="s">
         <v>32</v>
       </c>
@@ -8243,7 +8215,7 @@
       <c r="B164" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C164" s="20"/>
+      <c r="C164" s="28"/>
       <c r="D164" s="4" t="s">
         <v>32</v>
       </c>
@@ -8255,289 +8227,208 @@
       <c r="B165" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C165" s="21"/>
+      <c r="C165" s="29"/>
       <c r="D165" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="30" customHeight="1"/>
     <row r="167" spans="1:6" ht="30" customHeight="1">
-      <c r="A167" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="B167" s="29"/>
-      <c r="C167" s="29"/>
-      <c r="D167" s="27"/>
+      <c r="A167" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B167" s="23"/>
+      <c r="C167" s="23"/>
+      <c r="D167" s="24"/>
     </row>
     <row r="168" spans="1:6" ht="30" customHeight="1">
-      <c r="A168" s="24" t="s">
+      <c r="A168" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B168" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="C168" s="24" t="s">
+      <c r="B168" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C168" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D168" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="E168" s="24" t="s">
+      <c r="D168" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E168" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F168" s="28" t="s">
-        <v>151</v>
+      <c r="F168" s="16" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="30" customHeight="1">
       <c r="A169" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B169" s="1"/>
       <c r="C169" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D169" s="1"/>
       <c r="E169" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F169" s="1"/>
     </row>
     <row r="170" spans="1:6" ht="30" customHeight="1">
       <c r="A170" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D170" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E170" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="F170" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="30" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="30" customHeight="1">
       <c r="A172" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="30" customHeight="1">
       <c r="A173" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="30" customHeight="1">
+      <c r="A174" s="17"/>
+      <c r="B174" s="18"/>
+    </row>
+    <row r="175" spans="1:6" ht="30" customHeight="1">
+      <c r="A175" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B175" s="25"/>
+    </row>
+    <row r="176" spans="1:6" ht="30" customHeight="1">
+      <c r="A176" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B176" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="30" customHeight="1">
+      <c r="A177" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B177" s="1"/>
+    </row>
+    <row r="178" spans="1:2" ht="30" customHeight="1">
+      <c r="A178" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="30" customHeight="1">
+      <c r="A179" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="30" customHeight="1">
+      <c r="A180" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" ht="30" customHeight="1">
-      <c r="A174" s="30"/>
-      <c r="B174" s="31"/>
-    </row>
-    <row r="175" spans="1:6" ht="30" customHeight="1">
-      <c r="A175" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="B175" s="29"/>
-      <c r="C175" s="29"/>
-      <c r="D175" s="27"/>
-    </row>
-    <row r="176" spans="1:6" ht="30" customHeight="1">
-      <c r="A176" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B176" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="C176" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D176" s="28" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" ht="30" customHeight="1">
-      <c r="A177" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B177" s="1"/>
-      <c r="C177" s="2" t="s">
+      <c r="B180" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D177" s="1"/>
-    </row>
-    <row r="178" spans="1:4" ht="30" customHeight="1">
-      <c r="A178" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="30" customHeight="1">
-      <c r="A179" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" ht="30" customHeight="1">
-      <c r="A180" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" ht="30" customHeight="1">
+    </row>
+    <row r="181" spans="1:2" ht="30" customHeight="1">
       <c r="A181" s="2" t="s">
         <v>251</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" ht="30" customHeight="1"/>
-    <row r="183" spans="1:4" ht="30" customHeight="1">
-      <c r="A183" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B183" s="16"/>
-    </row>
-    <row r="184" spans="1:4" ht="30" customHeight="1">
-      <c r="A184" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B184" s="28" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" ht="30" customHeight="1">
-      <c r="A185" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B185" s="1"/>
-    </row>
-    <row r="186" spans="1:4" ht="30" customHeight="1">
-      <c r="A186" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" ht="30" customHeight="1">
-      <c r="A187" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="30" customHeight="1">
-      <c r="A188" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" ht="30" customHeight="1">
-      <c r="A189" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="30" customHeight="1">
-      <c r="A190" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="30" customHeight="1"/>
-    <row r="192" spans="1:4" ht="30" customHeight="1"/>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="30" customHeight="1">
+      <c r="A182" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="30" customHeight="1"/>
+    <row r="184" spans="1:2" ht="30" customHeight="1"/>
+    <row r="185" spans="1:2" ht="30" customHeight="1"/>
+    <row r="186" spans="1:2" ht="30" customHeight="1"/>
+    <row r="187" spans="1:2" ht="30" customHeight="1"/>
+    <row r="188" spans="1:2" ht="30" customHeight="1"/>
+    <row r="189" spans="1:2" ht="30" customHeight="1"/>
+    <row r="190" spans="1:2" ht="30" customHeight="1"/>
+    <row r="191" spans="1:2" ht="30" customHeight="1"/>
+    <row r="192" spans="1:2" ht="30" customHeight="1"/>
     <row r="193" ht="30" customHeight="1"/>
     <row r="194" ht="30" customHeight="1"/>
     <row r="195" ht="30" customHeight="1"/>
@@ -8579,26 +8470,32 @@
     <row r="231" ht="30" customHeight="1"/>
     <row r="232" ht="30" customHeight="1"/>
     <row r="233" ht="30" customHeight="1"/>
-    <row r="234" ht="30" customHeight="1"/>
-    <row r="235" ht="30" customHeight="1"/>
-    <row r="236" ht="30" customHeight="1"/>
-    <row r="237" ht="30" customHeight="1"/>
-    <row r="238" ht="30" customHeight="1"/>
-    <row r="239" ht="30" customHeight="1"/>
-    <row r="240" ht="30" customHeight="1"/>
-    <row r="241" ht="30" customHeight="1"/>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A167:D167"/>
-    <mergeCell ref="A175:D175"/>
-    <mergeCell ref="A183:B183"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B77:D77"/>
+  <mergeCells count="35">
+    <mergeCell ref="A136:D136"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="C146:C150"/>
+    <mergeCell ref="B152:D152"/>
+    <mergeCell ref="C161:C165"/>
+    <mergeCell ref="C101:C105"/>
+    <mergeCell ref="B107:D107"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="C56:C60"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="C11:C15"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="C26:C30"/>
     <mergeCell ref="B32:D32"/>
+    <mergeCell ref="A167:D167"/>
+    <mergeCell ref="A175:B175"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="C71:C75"/>
     <mergeCell ref="C116:C120"/>
     <mergeCell ref="B122:D122"/>
@@ -8610,21 +8507,6 @@
     <mergeCell ref="A121:D121"/>
     <mergeCell ref="C86:C90"/>
     <mergeCell ref="B92:D92"/>
-    <mergeCell ref="C101:C105"/>
-    <mergeCell ref="B107:D107"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="A136:D136"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="C146:C150"/>
-    <mergeCell ref="B152:D152"/>
-    <mergeCell ref="C161:C165"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8650,7 +8532,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>2</v>
@@ -8666,21 +8548,21 @@
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>39</v>
@@ -8688,10 +8570,10 @@
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
@@ -8700,19 +8582,19 @@
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>2</v>
@@ -8740,127 +8622,127 @@
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>51</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
       <c r="G15" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>2</v>
@@ -8894,137 +8776,137 @@
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E18" s="4"/>
       <c r="G18" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>51</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>51</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>51</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="G21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="J21" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="H22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
       <c r="J23" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>2</v>
@@ -9040,50 +8922,50 @@
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="30" customHeight="1"/>
     <row r="31" spans="1:11" ht="30" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>2</v>
@@ -9111,53 +8993,53 @@
     </row>
     <row r="33" spans="1:8" ht="30" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="4"/>
       <c r="D33" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>51</v>
@@ -9165,39 +9047,39 @@
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="E37" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>38</v>
@@ -9205,27 +9087,27 @@
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1">
       <c r="G38" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>2</v>
@@ -9253,53 +9135,53 @@
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E41" s="4"/>
       <c r="G41" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>51</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="30" customHeight="1">
       <c r="A43" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>51</v>
@@ -9307,67 +9189,67 @@
     </row>
     <row r="44" spans="1:8" ht="30" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="H44" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="30" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1">
       <c r="G46" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>2</v>
@@ -9395,56 +9277,56 @@
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B49" s="4"/>
       <c r="D49" s="4" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="E49" s="4"/>
       <c r="G49" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1">
@@ -9453,10 +9335,10 @@
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="G52" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1">
@@ -9465,10 +9347,10 @@
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="G53" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1">
@@ -9477,10 +9359,10 @@
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="G54" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="30" customHeight="1"/>
@@ -9564,35 +9446,35 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+        <v>209</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>160</v>
+      <c r="B2" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -9601,7 +9483,7 @@
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -9610,7 +9492,7 @@
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -9619,22 +9501,22 @@
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>162</v>
+        <v>159</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>160</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -9643,52 +9525,52 @@
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
+        <v>210</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
     </row>
     <row r="11" spans="1:5" ht="30" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>160</v>
+      <c r="B11" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -9697,7 +9579,7 @@
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -9706,7 +9588,7 @@
     </row>
     <row r="14" spans="1:5" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -9715,24 +9597,24 @@
     </row>
     <row r="15" spans="1:5" ht="30" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -9741,19 +9623,19 @@
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1"/>
